--- a/splithub_master_template_19.04.26.xlsx
+++ b/splithub_master_template_19.04.26.xlsx
@@ -498,31 +498,33 @@
   <dimension ref="A1:AA247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="8.5546875" customWidth="1" style="12" min="1" max="1"/>
-    <col width="7" bestFit="1" customWidth="1" style="12" min="2" max="2"/>
-    <col width="24.5546875" customWidth="1" style="10" min="3" max="3"/>
-    <col width="9.5546875" customWidth="1" style="10" min="4" max="4"/>
-    <col width="11" customWidth="1" style="10" min="5" max="5"/>
-    <col width="18.33203125" customWidth="1" style="10" min="6" max="6"/>
-    <col width="16.109375" customWidth="1" style="10" min="7" max="7"/>
-    <col width="10.44140625" customWidth="1" style="10" min="8" max="8"/>
-    <col width="8.6640625" customWidth="1" style="10" min="9" max="9"/>
-    <col width="12.6640625" customWidth="1" style="10" min="10" max="10"/>
-    <col width="6.6640625" customWidth="1" style="10" min="11" max="11"/>
-    <col width="9.6640625" customWidth="1" style="10" min="12" max="12"/>
-    <col width="8.5546875" customWidth="1" style="10" min="13" max="14"/>
-    <col width="9.5546875" bestFit="1" customWidth="1" style="10" min="15" max="15"/>
-    <col width="9.88671875" customWidth="1" style="10" min="16" max="16"/>
-    <col width="11.6640625" customWidth="1" style="10" min="17" max="17"/>
-    <col width="12" customWidth="1" style="10" min="18" max="18"/>
-    <col width="14.6640625" customWidth="1" style="4" min="19" max="19"/>
-    <col width="22.5546875" customWidth="1" style="4" min="20" max="20"/>
-    <col width="61.44140625" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="23.44140625" customWidth="1" min="23" max="23"/>
-    <col width="13.44140625" customWidth="1" min="24" max="24"/>
-    <col width="19.6640625" bestFit="1" customWidth="1" min="25" max="25"/>
-    <col width="11" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" style="12" min="1" max="1"/>
+    <col width="6" bestFit="1" customWidth="1" style="12" min="2" max="2"/>
+    <col width="34" customWidth="1" style="10" min="3" max="3"/>
+    <col width="12" customWidth="1" style="10" min="4" max="4"/>
+    <col width="27" customWidth="1" style="10" min="5" max="5"/>
+    <col width="32" customWidth="1" style="10" min="6" max="6"/>
+    <col width="47" customWidth="1" style="10" min="7" max="7"/>
+    <col width="15" customWidth="1" style="10" min="8" max="8"/>
+    <col width="7" customWidth="1" style="10" min="9" max="9"/>
+    <col width="10" customWidth="1" style="10" min="10" max="10"/>
+    <col width="7" customWidth="1" style="10" min="11" max="11"/>
+    <col width="10" customWidth="1" style="10" min="12" max="12"/>
+    <col width="5" customWidth="1" style="10" min="13" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="9" bestFit="1" customWidth="1" style="10" min="15" max="15"/>
+    <col width="8" customWidth="1" style="10" min="16" max="16"/>
+    <col width="14" customWidth="1" style="10" min="17" max="17"/>
+    <col width="18" customWidth="1" style="10" min="18" max="18"/>
+    <col width="54" customWidth="1" style="4" min="19" max="19"/>
+    <col width="60" customWidth="1" style="4" min="20" max="20"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="23"/>
+    <col width="32" customWidth="1" min="24" max="24"/>
+    <col width="12" bestFit="1" customWidth="1" min="25" max="25"/>
+    <col width="32" bestFit="1" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customFormat="1" customHeight="1" s="5">
@@ -29540,8 +29542,8 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29678,8 +29680,8 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29816,8 +29818,8 @@
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
